--- a/data/article_tables/data1.xlsx
+++ b/data/article_tables/data1.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F193FFC3-6904-40B6-8BE9-BF0261721013}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492F120B-1C20-4B56-B58A-CC62FCC80D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="697" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="697" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicative Elements" sheetId="4" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="Campbell and Healey 2016" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Milic 2014'!$A$1:$A$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Milic 2014'!$A$1:$A$21</definedName>
   </definedNames>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,14 +29,23 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="276">
   <si>
     <t>Method</t>
   </si>
@@ -126,21 +135,6 @@
   </si>
   <si>
     <t>Giali</t>
-  </si>
-  <si>
-    <t>Melos-Adamas</t>
-  </si>
-  <si>
-    <t>Melos-Demenegaki</t>
-  </si>
-  <si>
-    <t>Carpathian-1</t>
-  </si>
-  <si>
-    <t>Carpathian-2</t>
-  </si>
-  <si>
-    <t>Nenezi-Dag</t>
   </si>
   <si>
     <t>Cambell and Healey 2016</t>
@@ -931,6 +925,33 @@
   <si>
     <t>Brown
 Rhyolite</t>
+  </si>
+  <si>
+    <t>Ti (ppm)</t>
+  </si>
+  <si>
+    <t>Mn (ppm)</t>
+  </si>
+  <si>
+    <t>Fe (ppm)</t>
+  </si>
+  <si>
+    <t>Zn (ppm)</t>
+  </si>
+  <si>
+    <t>Sr (ppm)</t>
+  </si>
+  <si>
+    <t>Carpathian</t>
+  </si>
+  <si>
+    <t>Göllü Dag</t>
+  </si>
+  <si>
+    <t>Ba (ppm)</t>
+  </si>
+  <si>
+    <t>Pb (ppm)</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1394,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1388,7 +1409,7 @@
         <v>25</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>21</v>
@@ -1406,22 +1427,22 @@
         <v>24</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="Q1" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -1429,221 +1450,221 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
         <v>48</v>
       </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
       <c r="O10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="Q10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -1679,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1705,7 +1726,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -1757,16 +1778,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1775,41 +1796,41 @@
         <v>882</v>
       </c>
       <c r="G10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -1818,21 +1839,21 @@
         <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -1841,18 +1862,18 @@
         <v>873</v>
       </c>
       <c r="G17" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I17" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G18" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1862,21 +1883,21 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D21" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -1885,48 +1906,48 @@
         <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H21" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I21" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I22" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G23" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I23" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" t="s">
         <v>206</v>
       </c>
-      <c r="B25" t="s">
-        <v>207</v>
-      </c>
-      <c r="C25" t="s">
-        <v>211</v>
-      </c>
       <c r="D25" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -1935,39 +1956,39 @@
         <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H25" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H26" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G27" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G28" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1986,37 +2007,37 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" t="s">
         <v>96</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>97</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K1" t="s">
         <v>99</v>
-      </c>
-      <c r="F1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K1" t="s">
-        <v>104</v>
       </c>
       <c r="L1" t="s">
         <v>27</v>
@@ -2024,7 +2045,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B2">
         <v>447</v>
@@ -2057,12 +2078,12 @@
         <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B3">
         <v>591</v>
@@ -2095,12 +2116,12 @@
         <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B4">
         <v>422</v>
@@ -2133,12 +2154,12 @@
         <v>69</v>
       </c>
       <c r="L4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B5">
         <v>284</v>
@@ -2171,12 +2192,12 @@
         <v>18</v>
       </c>
       <c r="L5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B6">
         <v>515</v>
@@ -2209,12 +2230,12 @@
         <v>23</v>
       </c>
       <c r="L6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B7">
         <v>328</v>
@@ -2247,12 +2268,12 @@
         <v>21</v>
       </c>
       <c r="L7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B8">
         <v>572</v>
@@ -2285,12 +2306,12 @@
         <v>63</v>
       </c>
       <c r="L8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B9">
         <v>697</v>
@@ -2323,12 +2344,12 @@
         <v>62</v>
       </c>
       <c r="L9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B10">
         <v>384</v>
@@ -2361,12 +2382,12 @@
         <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B11">
         <v>338</v>
@@ -2399,12 +2420,12 @@
         <v>17</v>
       </c>
       <c r="L11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B12">
         <v>442</v>
@@ -2437,12 +2458,12 @@
         <v>21</v>
       </c>
       <c r="L12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B13">
         <v>633</v>
@@ -2475,12 +2496,12 @@
         <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B14">
         <v>421</v>
@@ -2513,12 +2534,12 @@
         <v>21</v>
       </c>
       <c r="L14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B15">
         <v>577</v>
@@ -2551,12 +2572,12 @@
         <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B16">
         <v>472</v>
@@ -2589,12 +2610,12 @@
         <v>77</v>
       </c>
       <c r="L16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B17">
         <v>577</v>
@@ -2627,12 +2648,12 @@
         <v>55</v>
       </c>
       <c r="L17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B18">
         <v>631</v>
@@ -2665,12 +2686,12 @@
         <v>59</v>
       </c>
       <c r="L18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B19">
         <v>395</v>
@@ -2703,12 +2724,12 @@
         <v>21</v>
       </c>
       <c r="L19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B20">
         <v>366</v>
@@ -2741,12 +2762,12 @@
         <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B21">
         <v>576</v>
@@ -2779,12 +2800,12 @@
         <v>63</v>
       </c>
       <c r="L21" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B22">
         <v>325</v>
@@ -2817,12 +2838,12 @@
         <v>17</v>
       </c>
       <c r="L22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B23">
         <v>396</v>
@@ -2855,12 +2876,12 @@
         <v>76</v>
       </c>
       <c r="L23" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B24">
         <v>370</v>
@@ -2893,12 +2914,12 @@
         <v>19</v>
       </c>
       <c r="L24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B25">
         <v>307</v>
@@ -2931,12 +2952,12 @@
         <v>19</v>
       </c>
       <c r="L25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B26">
         <v>516</v>
@@ -2969,12 +2990,12 @@
         <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B27">
         <v>296</v>
@@ -3007,12 +3028,12 @@
         <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B28">
         <v>311</v>
@@ -3045,12 +3066,12 @@
         <v>18</v>
       </c>
       <c r="L28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B29">
         <v>508</v>
@@ -3083,12 +3104,12 @@
         <v>23</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B30">
         <v>461</v>
@@ -3121,12 +3142,12 @@
         <v>71</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B31">
         <v>276</v>
@@ -3159,12 +3180,12 @@
         <v>16</v>
       </c>
       <c r="L31" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B32">
         <v>324</v>
@@ -3197,12 +3218,12 @@
         <v>22</v>
       </c>
       <c r="L32" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B33">
         <v>596</v>
@@ -3235,12 +3256,12 @@
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B34">
         <v>346</v>
@@ -3273,12 +3294,12 @@
         <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B35">
         <v>516</v>
@@ -3311,12 +3332,12 @@
         <v>79</v>
       </c>
       <c r="L35" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B36">
         <v>483</v>
@@ -3349,12 +3370,12 @@
         <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B37">
         <v>561</v>
@@ -3387,12 +3408,12 @@
         <v>60</v>
       </c>
       <c r="L37" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B38">
         <v>840</v>
@@ -3425,12 +3446,12 @@
         <v>75</v>
       </c>
       <c r="L38" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B39">
         <v>642</v>
@@ -3463,12 +3484,12 @@
         <v>60</v>
       </c>
       <c r="L39" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B40">
         <v>364</v>
@@ -3501,12 +3522,12 @@
         <v>23</v>
       </c>
       <c r="L40" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B41">
         <v>443</v>
@@ -3539,12 +3560,12 @@
         <v>24</v>
       </c>
       <c r="L41" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B42">
         <v>439</v>
@@ -3577,12 +3598,12 @@
         <v>23</v>
       </c>
       <c r="L42" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B43">
         <v>451</v>
@@ -3615,12 +3636,12 @@
         <v>73</v>
       </c>
       <c r="L43" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B44">
         <v>519</v>
@@ -3653,12 +3674,12 @@
         <v>82</v>
       </c>
       <c r="L44" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B45">
         <v>335</v>
@@ -3691,42 +3712,42 @@
         <v>16</v>
       </c>
       <c r="L45" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" t="s">
+        <v>95</v>
+      </c>
+      <c r="G49" t="s">
         <v>96</v>
       </c>
-      <c r="C49" t="s">
+      <c r="H49" t="s">
         <v>97</v>
       </c>
-      <c r="D49" t="s">
+      <c r="I49" t="s">
+        <v>100</v>
+      </c>
+      <c r="J49" t="s">
         <v>98</v>
       </c>
-      <c r="E49" t="s">
+      <c r="K49" t="s">
         <v>99</v>
-      </c>
-      <c r="F49" t="s">
-        <v>100</v>
-      </c>
-      <c r="G49" t="s">
-        <v>101</v>
-      </c>
-      <c r="H49" t="s">
-        <v>102</v>
-      </c>
-      <c r="I49" t="s">
-        <v>105</v>
-      </c>
-      <c r="J49" t="s">
-        <v>103</v>
-      </c>
-      <c r="K49" t="s">
-        <v>104</v>
       </c>
       <c r="L49" t="s">
         <v>27</v>
@@ -3734,7 +3755,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B50">
         <v>447</v>
@@ -3767,12 +3788,12 @@
         <v>30</v>
       </c>
       <c r="L50" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B51">
         <v>591</v>
@@ -3805,12 +3826,12 @@
         <v>33</v>
       </c>
       <c r="L51" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B52">
         <v>284</v>
@@ -3843,12 +3864,12 @@
         <v>18</v>
       </c>
       <c r="L52" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B53">
         <v>515</v>
@@ -3881,12 +3902,12 @@
         <v>23</v>
       </c>
       <c r="L53" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B54">
         <v>442</v>
@@ -3919,12 +3940,12 @@
         <v>21</v>
       </c>
       <c r="L54" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B55">
         <v>633</v>
@@ -3957,12 +3978,12 @@
         <v>26</v>
       </c>
       <c r="L55" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B56">
         <v>577</v>
@@ -3995,12 +4016,12 @@
         <v>25</v>
       </c>
       <c r="L56" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B57">
         <v>516</v>
@@ -4033,12 +4054,12 @@
         <v>25</v>
       </c>
       <c r="L57" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B58">
         <v>508</v>
@@ -4071,12 +4092,12 @@
         <v>23</v>
       </c>
       <c r="L58" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B59">
         <v>596</v>
@@ -4109,12 +4130,12 @@
         <v>28</v>
       </c>
       <c r="L59" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B60">
         <v>483</v>
@@ -4147,12 +4168,12 @@
         <v>21</v>
       </c>
       <c r="L60" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B61">
         <v>335</v>
@@ -4185,12 +4206,12 @@
         <v>16</v>
       </c>
       <c r="L61" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B62" s="3">
         <f>AVERAGE(B50:B61)</f>
@@ -4235,7 +4256,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B63">
         <f>MAX(B50:B62)</f>
@@ -4280,7 +4301,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B64">
         <f>MIN(B50:B61)</f>
@@ -4325,37 +4346,37 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
+        <v>91</v>
+      </c>
+      <c r="C67" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" t="s">
+        <v>95</v>
+      </c>
+      <c r="G67" t="s">
         <v>96</v>
       </c>
-      <c r="C67" t="s">
+      <c r="H67" t="s">
         <v>97</v>
       </c>
-      <c r="D67" t="s">
+      <c r="I67" t="s">
+        <v>100</v>
+      </c>
+      <c r="J67" t="s">
         <v>98</v>
       </c>
-      <c r="E67" t="s">
+      <c r="K67" t="s">
         <v>99</v>
-      </c>
-      <c r="F67" t="s">
-        <v>100</v>
-      </c>
-      <c r="G67" t="s">
-        <v>101</v>
-      </c>
-      <c r="H67" t="s">
-        <v>102</v>
-      </c>
-      <c r="I67" t="s">
-        <v>105</v>
-      </c>
-      <c r="J67" t="s">
-        <v>103</v>
-      </c>
-      <c r="K67" t="s">
-        <v>104</v>
       </c>
       <c r="L67" t="s">
         <v>27</v>
@@ -4363,7 +4384,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B68">
         <v>422</v>
@@ -4396,12 +4417,12 @@
         <v>69</v>
       </c>
       <c r="L68" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B69">
         <v>572</v>
@@ -4434,12 +4455,12 @@
         <v>63</v>
       </c>
       <c r="L69" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B70">
         <v>697</v>
@@ -4472,12 +4493,12 @@
         <v>62</v>
       </c>
       <c r="L70" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B71">
         <v>472</v>
@@ -4510,12 +4531,12 @@
         <v>77</v>
       </c>
       <c r="L71" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B72">
         <v>577</v>
@@ -4548,12 +4569,12 @@
         <v>55</v>
       </c>
       <c r="L72" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B73">
         <v>631</v>
@@ -4586,12 +4607,12 @@
         <v>59</v>
       </c>
       <c r="L73" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B74">
         <v>576</v>
@@ -4624,12 +4645,12 @@
         <v>63</v>
       </c>
       <c r="L74" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B75">
         <v>396</v>
@@ -4662,12 +4683,12 @@
         <v>76</v>
       </c>
       <c r="L75" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B76">
         <v>461</v>
@@ -4700,12 +4721,12 @@
         <v>71</v>
       </c>
       <c r="L76" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B77">
         <v>516</v>
@@ -4738,12 +4759,12 @@
         <v>79</v>
       </c>
       <c r="L77" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B78">
         <v>561</v>
@@ -4776,12 +4797,12 @@
         <v>60</v>
       </c>
       <c r="L78" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B79">
         <v>840</v>
@@ -4814,12 +4835,12 @@
         <v>75</v>
       </c>
       <c r="L79" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B80">
         <v>642</v>
@@ -4852,12 +4873,12 @@
         <v>60</v>
       </c>
       <c r="L80" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B81">
         <v>451</v>
@@ -4890,12 +4911,12 @@
         <v>73</v>
       </c>
       <c r="L81" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B82">
         <v>519</v>
@@ -4928,12 +4949,12 @@
         <v>82</v>
       </c>
       <c r="L82" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B83" s="3">
         <f>AVERAGE(B68:B82)</f>
@@ -4978,7 +4999,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B84">
         <f>MAX(B68:B83)</f>
@@ -5023,7 +5044,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B85">
         <f>MIN(B68:B82)</f>
@@ -5068,42 +5089,42 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B88" t="s">
+        <v>91</v>
+      </c>
+      <c r="C88" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" t="s">
+        <v>93</v>
+      </c>
+      <c r="E88" t="s">
+        <v>94</v>
+      </c>
+      <c r="F88" t="s">
+        <v>95</v>
+      </c>
+      <c r="G88" t="s">
         <v>96</v>
       </c>
-      <c r="C88" t="s">
+      <c r="H88" t="s">
         <v>97</v>
       </c>
-      <c r="D88" t="s">
+      <c r="I88" t="s">
+        <v>100</v>
+      </c>
+      <c r="J88" t="s">
         <v>98</v>
       </c>
-      <c r="E88" t="s">
+      <c r="K88" t="s">
         <v>99</v>
-      </c>
-      <c r="F88" t="s">
-        <v>100</v>
-      </c>
-      <c r="G88" t="s">
-        <v>101</v>
-      </c>
-      <c r="H88" t="s">
-        <v>102</v>
-      </c>
-      <c r="I88" t="s">
-        <v>105</v>
-      </c>
-      <c r="J88" t="s">
-        <v>103</v>
-      </c>
-      <c r="K88" t="s">
-        <v>104</v>
       </c>
       <c r="L88" t="s">
         <v>27</v>
@@ -5111,7 +5132,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B89">
         <v>328</v>
@@ -5144,12 +5165,12 @@
         <v>21</v>
       </c>
       <c r="L89" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B90">
         <v>384</v>
@@ -5182,12 +5203,12 @@
         <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B91">
         <v>338</v>
@@ -5220,12 +5241,12 @@
         <v>17</v>
       </c>
       <c r="L91" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B92">
         <v>421</v>
@@ -5258,12 +5279,12 @@
         <v>21</v>
       </c>
       <c r="L92" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B93">
         <v>395</v>
@@ -5296,12 +5317,12 @@
         <v>21</v>
       </c>
       <c r="L93" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B94">
         <v>366</v>
@@ -5334,12 +5355,12 @@
         <v>20</v>
       </c>
       <c r="L94" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B95">
         <v>325</v>
@@ -5372,12 +5393,12 @@
         <v>17</v>
       </c>
       <c r="L95" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B96">
         <v>370</v>
@@ -5410,12 +5431,12 @@
         <v>19</v>
       </c>
       <c r="L96" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B97">
         <v>307</v>
@@ -5448,12 +5469,12 @@
         <v>19</v>
       </c>
       <c r="L97" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B98">
         <v>296</v>
@@ -5486,12 +5507,12 @@
         <v>20</v>
       </c>
       <c r="L98" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B99">
         <v>311</v>
@@ -5524,12 +5545,12 @@
         <v>18</v>
       </c>
       <c r="L99" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B100">
         <v>276</v>
@@ -5562,12 +5583,12 @@
         <v>16</v>
       </c>
       <c r="L100" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B101">
         <v>324</v>
@@ -5600,12 +5621,12 @@
         <v>22</v>
       </c>
       <c r="L101" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B102">
         <v>346</v>
@@ -5638,12 +5659,12 @@
         <v>20</v>
       </c>
       <c r="L102" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B103">
         <v>364</v>
@@ -5676,12 +5697,12 @@
         <v>23</v>
       </c>
       <c r="L103" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B104">
         <v>443</v>
@@ -5714,12 +5735,12 @@
         <v>24</v>
       </c>
       <c r="L104" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B105">
         <v>439</v>
@@ -5752,12 +5773,12 @@
         <v>23</v>
       </c>
       <c r="L105" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B106" s="3">
         <f>AVERAGE(B89:B105)</f>
@@ -5802,7 +5823,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B107">
         <f>MAX(B89:B106)</f>
@@ -5847,7 +5868,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B108">
         <f>MIN(B89:B105)</f>
@@ -5898,7 +5919,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AL42"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -5930,121 +5951,37 @@
     <col min="29" max="29" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD1">
-        <v>859</v>
-      </c>
-      <c r="AE1">
-        <v>439</v>
-      </c>
-      <c r="AF1">
-        <v>6779</v>
-      </c>
-      <c r="AG1">
-        <v>32</v>
-      </c>
-      <c r="AH1">
-        <v>155</v>
-      </c>
-      <c r="AI1">
-        <v>99</v>
-      </c>
-      <c r="AJ1">
-        <v>137</v>
-      </c>
-      <c r="AK1">
-        <v>420</v>
-      </c>
-      <c r="AL1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>178</v>
-      </c>
-      <c r="H2">
-        <v>12</v>
-      </c>
-      <c r="I2">
-        <v>74</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD2">
-        <v>807</v>
-      </c>
-      <c r="AE2">
-        <v>431</v>
-      </c>
-      <c r="AF2">
-        <v>6203</v>
-      </c>
-      <c r="AG2">
-        <v>34</v>
-      </c>
-      <c r="AH2">
-        <v>156</v>
-      </c>
-      <c r="AI2">
-        <v>98</v>
-      </c>
-      <c r="AJ2">
-        <v>135</v>
-      </c>
-      <c r="AK2">
-        <v>396</v>
-      </c>
-      <c r="AL2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>178</v>
@@ -6055,108 +5992,24 @@
       <c r="D3">
         <v>74</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3">
-        <v>152</v>
-      </c>
-      <c r="H3">
-        <v>99</v>
-      </c>
-      <c r="I3">
-        <v>136</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD3">
-        <v>843</v>
-      </c>
-      <c r="AE3">
-        <v>440</v>
-      </c>
-      <c r="AF3">
-        <v>5821</v>
-      </c>
-      <c r="AG3">
-        <v>28</v>
-      </c>
-      <c r="AH3">
-        <v>107</v>
-      </c>
-      <c r="AI3">
-        <v>102</v>
-      </c>
-      <c r="AJ3">
-        <v>105</v>
-      </c>
-      <c r="AK3">
-        <v>405</v>
-      </c>
-      <c r="AL3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4">
-        <v>108</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4">
-        <v>107</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD4">
-        <v>830</v>
-      </c>
-      <c r="AE4">
-        <v>400</v>
-      </c>
-      <c r="AF4">
-        <v>5672</v>
-      </c>
-      <c r="AG4">
-        <v>26</v>
-      </c>
-      <c r="AH4">
-        <v>112</v>
-      </c>
-      <c r="AI4">
-        <v>97</v>
-      </c>
-      <c r="AJ4">
-        <v>111</v>
-      </c>
-      <c r="AK4">
-        <v>280</v>
-      </c>
-      <c r="AL4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B5">
         <v>152</v>
@@ -6167,108 +6020,24 @@
       <c r="D5">
         <v>136</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5">
-        <v>97</v>
-      </c>
-      <c r="H5">
-        <v>110</v>
-      </c>
-      <c r="I5">
-        <v>114</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD5">
-        <v>954</v>
-      </c>
-      <c r="AE5">
-        <v>446</v>
-      </c>
-      <c r="AF5">
-        <v>5882</v>
-      </c>
-      <c r="AG5">
-        <v>25</v>
-      </c>
-      <c r="AH5">
-        <v>111</v>
-      </c>
-      <c r="AI5">
-        <v>99</v>
-      </c>
-      <c r="AJ5">
-        <v>108</v>
-      </c>
-      <c r="AK5">
-        <v>338</v>
-      </c>
-      <c r="AL5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G6">
-        <v>367</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>128</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD6">
-        <v>892</v>
-      </c>
-      <c r="AE6">
-        <v>442</v>
-      </c>
-      <c r="AF6">
-        <v>5859</v>
-      </c>
-      <c r="AG6">
-        <v>24</v>
-      </c>
-      <c r="AH6">
-        <v>110</v>
-      </c>
-      <c r="AI6">
-        <v>103</v>
-      </c>
-      <c r="AJ6">
-        <v>110</v>
-      </c>
-      <c r="AK6">
-        <v>369</v>
-      </c>
-      <c r="AL6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>108</v>
@@ -6279,108 +6048,24 @@
       <c r="D7">
         <v>107</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7">
-        <v>121</v>
-      </c>
-      <c r="H7">
-        <v>63</v>
-      </c>
-      <c r="I7">
-        <v>96</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD7">
-        <v>827</v>
-      </c>
-      <c r="AE7">
-        <v>412</v>
-      </c>
-      <c r="AF7">
-        <v>5583</v>
-      </c>
-      <c r="AG7">
-        <v>27</v>
-      </c>
-      <c r="AH7">
-        <v>108</v>
-      </c>
-      <c r="AI7">
-        <v>107</v>
-      </c>
-      <c r="AJ7">
-        <v>107</v>
-      </c>
-      <c r="AK7">
-        <v>322</v>
-      </c>
-      <c r="AL7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8">
-        <v>163</v>
-      </c>
-      <c r="H8">
-        <v>72</v>
-      </c>
-      <c r="I8">
-        <v>67</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD8">
-        <v>830</v>
-      </c>
-      <c r="AE8">
-        <v>392</v>
-      </c>
-      <c r="AF8">
-        <v>5460</v>
-      </c>
-      <c r="AG8">
-        <v>24</v>
-      </c>
-      <c r="AH8">
-        <v>103</v>
-      </c>
-      <c r="AI8">
-        <v>98</v>
-      </c>
-      <c r="AJ8">
-        <v>104</v>
-      </c>
-      <c r="AK8">
-        <v>310</v>
-      </c>
-      <c r="AL8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B9">
         <v>97</v>
@@ -6391,52 +6076,10 @@
       <c r="D9">
         <v>114</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G9">
-        <v>175</v>
-      </c>
-      <c r="H9">
-        <v>73</v>
-      </c>
-      <c r="I9">
-        <v>127</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD9">
-        <v>874</v>
-      </c>
-      <c r="AE9">
-        <v>417</v>
-      </c>
-      <c r="AF9">
-        <v>5171</v>
-      </c>
-      <c r="AG9">
-        <v>27</v>
-      </c>
-      <c r="AH9">
-        <v>111</v>
-      </c>
-      <c r="AI9">
-        <v>93</v>
-      </c>
-      <c r="AJ9">
-        <v>109</v>
-      </c>
-      <c r="AK9">
-        <v>336</v>
-      </c>
-      <c r="AL9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>367</v>
@@ -6447,84 +6090,24 @@
       <c r="D10">
         <v>128</v>
       </c>
-      <c r="AC10" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD10">
-        <v>913</v>
-      </c>
-      <c r="AE10">
-        <v>427</v>
-      </c>
-      <c r="AF10">
-        <v>5618</v>
-      </c>
-      <c r="AG10">
-        <v>21</v>
-      </c>
-      <c r="AH10">
-        <v>105</v>
-      </c>
-      <c r="AI10">
-        <v>98</v>
-      </c>
-      <c r="AJ10">
-        <v>102</v>
-      </c>
-      <c r="AK10">
-        <v>407</v>
-      </c>
-      <c r="AL10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD11">
-        <v>1158</v>
-      </c>
-      <c r="AE11">
-        <v>354</v>
-      </c>
-      <c r="AF11">
-        <v>7231</v>
-      </c>
-      <c r="AG11">
-        <v>20</v>
-      </c>
-      <c r="AH11">
-        <v>97</v>
-      </c>
-      <c r="AI11">
-        <v>109</v>
-      </c>
-      <c r="AJ11">
-        <v>117</v>
-      </c>
-      <c r="AK11">
-        <v>339</v>
-      </c>
-      <c r="AL11">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B12">
         <v>121</v>
@@ -6535,84 +6118,24 @@
       <c r="D12">
         <v>96</v>
       </c>
-      <c r="AC12" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD12">
-        <v>1146</v>
-      </c>
-      <c r="AE12">
-        <v>399</v>
-      </c>
-      <c r="AF12">
-        <v>6902</v>
-      </c>
-      <c r="AG12">
-        <v>20</v>
-      </c>
-      <c r="AH12">
-        <v>97</v>
-      </c>
-      <c r="AI12">
-        <v>105</v>
-      </c>
-      <c r="AJ12">
-        <v>110</v>
-      </c>
-      <c r="AK12">
-        <v>315</v>
-      </c>
-      <c r="AL12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD13">
-        <v>1162</v>
-      </c>
-      <c r="AE13">
-        <v>390</v>
-      </c>
-      <c r="AF13">
-        <v>6997</v>
-      </c>
-      <c r="AG13">
-        <v>27</v>
-      </c>
-      <c r="AH13">
-        <v>95</v>
-      </c>
-      <c r="AI13">
-        <v>105</v>
-      </c>
-      <c r="AJ13">
-        <v>112</v>
-      </c>
-      <c r="AK13">
-        <v>378</v>
-      </c>
-      <c r="AL13">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B14">
         <v>163</v>
@@ -6623,84 +6146,24 @@
       <c r="D14">
         <v>67</v>
       </c>
-      <c r="AC14" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD14">
-        <v>1125</v>
-      </c>
-      <c r="AE14">
-        <v>381</v>
-      </c>
-      <c r="AF14">
-        <v>7166</v>
-      </c>
-      <c r="AG14">
-        <v>33</v>
-      </c>
-      <c r="AH14">
-        <v>98</v>
-      </c>
-      <c r="AI14">
-        <v>109</v>
-      </c>
-      <c r="AJ14">
-        <v>109</v>
-      </c>
-      <c r="AK14">
-        <v>255</v>
-      </c>
-      <c r="AL14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD15">
-        <v>1113</v>
-      </c>
-      <c r="AE15">
-        <v>379</v>
-      </c>
-      <c r="AF15">
-        <v>6849</v>
-      </c>
-      <c r="AG15">
-        <v>29</v>
-      </c>
-      <c r="AH15">
-        <v>95</v>
-      </c>
-      <c r="AI15">
-        <v>108</v>
-      </c>
-      <c r="AJ15">
-        <v>114</v>
-      </c>
-      <c r="AK15">
-        <v>312</v>
-      </c>
-      <c r="AL15">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B16">
         <v>175</v>
@@ -6711,866 +6174,1754 @@
       <c r="D16">
         <v>127</v>
       </c>
-      <c r="AC16" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D20" t="s">
+        <v>269</v>
+      </c>
+      <c r="E20" t="s">
+        <v>270</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H20" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" t="s">
+        <v>274</v>
+      </c>
+      <c r="J20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B21">
+        <v>298</v>
+      </c>
+      <c r="C21">
+        <v>466</v>
+      </c>
+      <c r="D21">
+        <v>4414</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+      <c r="F21">
+        <v>194</v>
+      </c>
+      <c r="G21">
+        <v>11</v>
+      </c>
+      <c r="H21">
+        <v>76</v>
+      </c>
+      <c r="I21">
+        <v>124</v>
+      </c>
+      <c r="J21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22">
+        <v>312</v>
+      </c>
+      <c r="C22">
+        <v>430</v>
+      </c>
+      <c r="D22">
+        <v>3891</v>
+      </c>
+      <c r="E22">
+        <v>17</v>
+      </c>
+      <c r="F22">
+        <v>179</v>
+      </c>
+      <c r="G22">
+        <v>11</v>
+      </c>
+      <c r="H22">
+        <v>75</v>
+      </c>
+      <c r="I22">
+        <v>117</v>
+      </c>
+      <c r="J22">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>273</v>
+      </c>
+      <c r="B23">
+        <v>229</v>
+      </c>
+      <c r="C23">
+        <v>463</v>
+      </c>
+      <c r="D23">
+        <v>4225</v>
+      </c>
+      <c r="E23">
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>187</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+      <c r="H23">
+        <v>74</v>
+      </c>
+      <c r="I23">
+        <v>142</v>
+      </c>
+      <c r="J23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>273</v>
+      </c>
+      <c r="B24">
+        <v>307</v>
+      </c>
+      <c r="C24">
+        <v>455</v>
+      </c>
+      <c r="D24">
+        <v>4066</v>
+      </c>
+      <c r="E24">
+        <v>14</v>
+      </c>
+      <c r="F24">
+        <v>178</v>
+      </c>
+      <c r="G24">
+        <v>14</v>
+      </c>
+      <c r="H24">
+        <v>75</v>
+      </c>
+      <c r="I24">
+        <v>123</v>
+      </c>
+      <c r="J24">
         <v>31</v>
       </c>
-      <c r="AD16">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>273</v>
+      </c>
+      <c r="B25">
+        <v>237</v>
+      </c>
+      <c r="C25">
+        <v>421</v>
+      </c>
+      <c r="D25">
+        <v>3868</v>
+      </c>
+      <c r="E25">
+        <v>17</v>
+      </c>
+      <c r="F25">
+        <v>176</v>
+      </c>
+      <c r="G25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <v>76</v>
+      </c>
+      <c r="I25">
+        <v>107</v>
+      </c>
+      <c r="J25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B26">
+        <v>417</v>
+      </c>
+      <c r="C26">
+        <v>425</v>
+      </c>
+      <c r="D26">
+        <v>3949</v>
+      </c>
+      <c r="E26">
+        <v>14</v>
+      </c>
+      <c r="F26">
+        <v>168</v>
+      </c>
+      <c r="G26">
+        <v>14</v>
+      </c>
+      <c r="H26">
+        <v>71</v>
+      </c>
+      <c r="I26">
+        <v>130</v>
+      </c>
+      <c r="J26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B27">
+        <v>573</v>
+      </c>
+      <c r="C27">
+        <v>344</v>
+      </c>
+      <c r="D27">
+        <v>4196</v>
+      </c>
+      <c r="E27">
+        <v>20</v>
+      </c>
+      <c r="F27">
+        <v>166</v>
+      </c>
+      <c r="G27">
+        <v>16</v>
+      </c>
+      <c r="H27">
+        <v>69</v>
+      </c>
+      <c r="I27">
+        <v>159</v>
+      </c>
+      <c r="J27">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>773</v>
+      </c>
+      <c r="C28">
+        <v>497</v>
+      </c>
+      <c r="D28">
+        <v>6653</v>
+      </c>
+      <c r="E28">
+        <v>34</v>
+      </c>
+      <c r="F28">
+        <v>158</v>
+      </c>
+      <c r="G28">
+        <v>99</v>
+      </c>
+      <c r="H28">
+        <v>137</v>
+      </c>
+      <c r="I28">
+        <v>380</v>
+      </c>
+      <c r="J28">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>812</v>
+      </c>
+      <c r="C29">
+        <v>455</v>
+      </c>
+      <c r="D29">
+        <v>6093</v>
+      </c>
+      <c r="E29">
+        <v>33</v>
+      </c>
+      <c r="F29">
+        <v>148</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
+      </c>
+      <c r="H29">
+        <v>137</v>
+      </c>
+      <c r="I29">
+        <v>374</v>
+      </c>
+      <c r="J29">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30">
+        <v>514</v>
+      </c>
+      <c r="C30">
+        <v>456</v>
+      </c>
+      <c r="D30">
+        <v>5557</v>
+      </c>
+      <c r="E30">
+        <v>29</v>
+      </c>
+      <c r="F30">
+        <v>143</v>
+      </c>
+      <c r="G30">
+        <v>97</v>
+      </c>
+      <c r="H30">
+        <v>132</v>
+      </c>
+      <c r="I30">
+        <v>413</v>
+      </c>
+      <c r="J30">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <v>859</v>
+      </c>
+      <c r="C31">
+        <v>439</v>
+      </c>
+      <c r="D31">
+        <v>6779</v>
+      </c>
+      <c r="E31">
+        <v>32</v>
+      </c>
+      <c r="F31">
+        <v>155</v>
+      </c>
+      <c r="G31">
+        <v>99</v>
+      </c>
+      <c r="H31">
+        <v>137</v>
+      </c>
+      <c r="I31">
+        <v>420</v>
+      </c>
+      <c r="J31">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32">
+        <v>807</v>
+      </c>
+      <c r="C32">
+        <v>431</v>
+      </c>
+      <c r="D32">
+        <v>6203</v>
+      </c>
+      <c r="E32">
+        <v>34</v>
+      </c>
+      <c r="F32">
+        <v>156</v>
+      </c>
+      <c r="G32">
+        <v>98</v>
+      </c>
+      <c r="H32">
+        <v>135</v>
+      </c>
+      <c r="I32">
+        <v>396</v>
+      </c>
+      <c r="J32">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33">
+        <v>843</v>
+      </c>
+      <c r="C33">
+        <v>440</v>
+      </c>
+      <c r="D33">
+        <v>5821</v>
+      </c>
+      <c r="E33">
+        <v>28</v>
+      </c>
+      <c r="F33">
+        <v>107</v>
+      </c>
+      <c r="G33">
+        <v>102</v>
+      </c>
+      <c r="H33">
+        <v>105</v>
+      </c>
+      <c r="I33">
+        <v>405</v>
+      </c>
+      <c r="J33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34">
+        <v>830</v>
+      </c>
+      <c r="C34">
+        <v>400</v>
+      </c>
+      <c r="D34">
+        <v>5672</v>
+      </c>
+      <c r="E34">
+        <v>26</v>
+      </c>
+      <c r="F34">
+        <v>112</v>
+      </c>
+      <c r="G34">
+        <v>97</v>
+      </c>
+      <c r="H34">
+        <v>111</v>
+      </c>
+      <c r="I34">
+        <v>280</v>
+      </c>
+      <c r="J34">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35">
+        <v>954</v>
+      </c>
+      <c r="C35">
+        <v>446</v>
+      </c>
+      <c r="D35">
+        <v>5882</v>
+      </c>
+      <c r="E35">
+        <v>25</v>
+      </c>
+      <c r="F35">
+        <v>111</v>
+      </c>
+      <c r="G35">
+        <v>99</v>
+      </c>
+      <c r="H35">
+        <v>108</v>
+      </c>
+      <c r="I35">
+        <v>338</v>
+      </c>
+      <c r="J35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36">
+        <v>892</v>
+      </c>
+      <c r="C36">
+        <v>442</v>
+      </c>
+      <c r="D36">
+        <v>5859</v>
+      </c>
+      <c r="E36">
+        <v>24</v>
+      </c>
+      <c r="F36">
+        <v>110</v>
+      </c>
+      <c r="G36">
+        <v>103</v>
+      </c>
+      <c r="H36">
+        <v>110</v>
+      </c>
+      <c r="I36">
+        <v>369</v>
+      </c>
+      <c r="J36">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37">
+        <v>827</v>
+      </c>
+      <c r="C37">
+        <v>412</v>
+      </c>
+      <c r="D37">
+        <v>5583</v>
+      </c>
+      <c r="E37">
+        <v>27</v>
+      </c>
+      <c r="F37">
+        <v>108</v>
+      </c>
+      <c r="G37">
+        <v>107</v>
+      </c>
+      <c r="H37">
+        <v>107</v>
+      </c>
+      <c r="I37">
+        <v>322</v>
+      </c>
+      <c r="J37">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38">
+        <v>830</v>
+      </c>
+      <c r="C38">
+        <v>392</v>
+      </c>
+      <c r="D38">
+        <v>5460</v>
+      </c>
+      <c r="E38">
+        <v>24</v>
+      </c>
+      <c r="F38">
+        <v>103</v>
+      </c>
+      <c r="G38">
+        <v>98</v>
+      </c>
+      <c r="H38">
+        <v>104</v>
+      </c>
+      <c r="I38">
+        <v>310</v>
+      </c>
+      <c r="J38">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39">
+        <v>874</v>
+      </c>
+      <c r="C39">
+        <v>417</v>
+      </c>
+      <c r="D39">
+        <v>5171</v>
+      </c>
+      <c r="E39">
+        <v>27</v>
+      </c>
+      <c r="F39">
+        <v>111</v>
+      </c>
+      <c r="G39">
+        <v>93</v>
+      </c>
+      <c r="H39">
+        <v>109</v>
+      </c>
+      <c r="I39">
+        <v>336</v>
+      </c>
+      <c r="J39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40">
+        <v>913</v>
+      </c>
+      <c r="C40">
+        <v>427</v>
+      </c>
+      <c r="D40">
+        <v>5618</v>
+      </c>
+      <c r="E40">
+        <v>21</v>
+      </c>
+      <c r="F40">
+        <v>105</v>
+      </c>
+      <c r="G40">
+        <v>98</v>
+      </c>
+      <c r="H40">
+        <v>102</v>
+      </c>
+      <c r="I40">
+        <v>407</v>
+      </c>
+      <c r="J40">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41">
+        <v>1158</v>
+      </c>
+      <c r="C41">
+        <v>354</v>
+      </c>
+      <c r="D41">
+        <v>7231</v>
+      </c>
+      <c r="E41">
+        <v>20</v>
+      </c>
+      <c r="F41">
+        <v>97</v>
+      </c>
+      <c r="G41">
+        <v>109</v>
+      </c>
+      <c r="H41">
+        <v>117</v>
+      </c>
+      <c r="I41">
+        <v>339</v>
+      </c>
+      <c r="J41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42">
+        <v>1146</v>
+      </c>
+      <c r="C42">
+        <v>399</v>
+      </c>
+      <c r="D42">
+        <v>6902</v>
+      </c>
+      <c r="E42">
+        <v>20</v>
+      </c>
+      <c r="F42">
+        <v>97</v>
+      </c>
+      <c r="G42">
+        <v>105</v>
+      </c>
+      <c r="H42">
+        <v>110</v>
+      </c>
+      <c r="I42">
+        <v>315</v>
+      </c>
+      <c r="J42">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43">
+        <v>1162</v>
+      </c>
+      <c r="C43">
+        <v>390</v>
+      </c>
+      <c r="D43">
+        <v>6997</v>
+      </c>
+      <c r="E43">
+        <v>27</v>
+      </c>
+      <c r="F43">
+        <v>95</v>
+      </c>
+      <c r="G43">
+        <v>105</v>
+      </c>
+      <c r="H43">
+        <v>112</v>
+      </c>
+      <c r="I43">
+        <v>378</v>
+      </c>
+      <c r="J43">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44">
+        <v>1125</v>
+      </c>
+      <c r="C44">
+        <v>381</v>
+      </c>
+      <c r="D44">
+        <v>7166</v>
+      </c>
+      <c r="E44">
+        <v>33</v>
+      </c>
+      <c r="F44">
+        <v>98</v>
+      </c>
+      <c r="G44">
+        <v>109</v>
+      </c>
+      <c r="H44">
+        <v>109</v>
+      </c>
+      <c r="I44">
+        <v>255</v>
+      </c>
+      <c r="J44">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45">
+        <v>1113</v>
+      </c>
+      <c r="C45">
+        <v>379</v>
+      </c>
+      <c r="D45">
+        <v>6849</v>
+      </c>
+      <c r="E45">
+        <v>29</v>
+      </c>
+      <c r="F45">
+        <v>95</v>
+      </c>
+      <c r="G45">
+        <v>108</v>
+      </c>
+      <c r="H45">
+        <v>114</v>
+      </c>
+      <c r="I45">
+        <v>312</v>
+      </c>
+      <c r="J45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46">
         <v>1145</v>
       </c>
-      <c r="AE16">
+      <c r="C46">
         <v>369</v>
       </c>
-      <c r="AF16">
+      <c r="D46">
         <v>6824</v>
       </c>
-      <c r="AG16">
+      <c r="E46">
         <v>27</v>
       </c>
-      <c r="AH16">
+      <c r="F46">
         <v>91</v>
       </c>
-      <c r="AI16">
+      <c r="G46">
         <v>106</v>
       </c>
-      <c r="AJ16">
+      <c r="H46">
         <v>112</v>
       </c>
-      <c r="AK16">
+      <c r="I46">
         <v>309</v>
       </c>
-      <c r="AL16">
+      <c r="J46">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC17" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47">
+        <v>1294</v>
+      </c>
+      <c r="C47">
+        <v>374</v>
+      </c>
+      <c r="D47">
+        <v>7191</v>
+      </c>
+      <c r="E47">
+        <v>25</v>
+      </c>
+      <c r="F47">
+        <v>98</v>
+      </c>
+      <c r="G47">
+        <v>114</v>
+      </c>
+      <c r="H47">
+        <v>108</v>
+      </c>
+      <c r="I47">
+        <v>304</v>
+      </c>
+      <c r="J47">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48">
+        <v>1125</v>
+      </c>
+      <c r="C48">
+        <v>432</v>
+      </c>
+      <c r="D48">
+        <v>7276</v>
+      </c>
+      <c r="E48">
+        <v>32</v>
+      </c>
+      <c r="F48">
+        <v>99</v>
+      </c>
+      <c r="G48">
+        <v>110</v>
+      </c>
+      <c r="H48">
+        <v>121</v>
+      </c>
+      <c r="I48">
+        <v>358</v>
+      </c>
+      <c r="J48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49">
+        <v>1149</v>
+      </c>
+      <c r="C49">
+        <v>374</v>
+      </c>
+      <c r="D49">
+        <v>6873</v>
+      </c>
+      <c r="E49">
+        <v>32</v>
+      </c>
+      <c r="F49">
+        <v>96</v>
+      </c>
+      <c r="G49">
+        <v>114</v>
+      </c>
+      <c r="H49">
+        <v>115</v>
+      </c>
+      <c r="I49">
+        <v>315</v>
+      </c>
+      <c r="J49">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50">
+        <v>1163</v>
+      </c>
+      <c r="C50">
+        <v>384</v>
+      </c>
+      <c r="D50">
+        <v>7056</v>
+      </c>
+      <c r="E50">
+        <v>27</v>
+      </c>
+      <c r="F50">
+        <v>98</v>
+      </c>
+      <c r="G50">
+        <v>111</v>
+      </c>
+      <c r="H50">
+        <v>119</v>
+      </c>
+      <c r="I50">
+        <v>323</v>
+      </c>
+      <c r="J50">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51">
+        <v>1206</v>
+      </c>
+      <c r="C51">
+        <v>412</v>
+      </c>
+      <c r="D51">
+        <v>7218</v>
+      </c>
+      <c r="E51">
+        <v>22</v>
+      </c>
+      <c r="F51">
+        <v>103</v>
+      </c>
+      <c r="G51">
+        <v>114</v>
+      </c>
+      <c r="H51">
+        <v>121</v>
+      </c>
+      <c r="I51">
+        <v>365</v>
+      </c>
+      <c r="J51">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52">
+        <v>776</v>
+      </c>
+      <c r="C52">
+        <v>251</v>
+      </c>
+      <c r="D52">
+        <v>5111</v>
+      </c>
+      <c r="E52">
+        <v>18</v>
+      </c>
+      <c r="F52">
+        <v>122</v>
+      </c>
+      <c r="G52">
+        <v>62</v>
+      </c>
+      <c r="H52">
+        <v>99</v>
+      </c>
+      <c r="I52">
+        <v>509</v>
+      </c>
+      <c r="J52">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53">
+        <v>674</v>
+      </c>
+      <c r="C53">
+        <v>257</v>
+      </c>
+      <c r="D53">
+        <v>4552</v>
+      </c>
+      <c r="E53">
+        <v>21</v>
+      </c>
+      <c r="F53">
+        <v>124</v>
+      </c>
+      <c r="G53">
+        <v>60</v>
+      </c>
+      <c r="H53">
+        <v>94</v>
+      </c>
+      <c r="I53">
+        <v>552</v>
+      </c>
+      <c r="J53">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54">
+        <v>560</v>
+      </c>
+      <c r="C54">
+        <v>219</v>
+      </c>
+      <c r="D54">
+        <v>4221</v>
+      </c>
+      <c r="E54">
+        <v>17</v>
+      </c>
+      <c r="F54">
+        <v>118</v>
+      </c>
+      <c r="G54">
+        <v>66</v>
+      </c>
+      <c r="H54">
+        <v>97</v>
+      </c>
+      <c r="I54">
+        <v>420</v>
+      </c>
+      <c r="J54">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55">
+        <v>544</v>
+      </c>
+      <c r="C55">
+        <v>239</v>
+      </c>
+      <c r="D55">
+        <v>4513</v>
+      </c>
+      <c r="E55">
+        <v>18</v>
+      </c>
+      <c r="F55">
+        <v>122</v>
+      </c>
+      <c r="G55">
+        <v>64</v>
+      </c>
+      <c r="H55">
+        <v>95</v>
+      </c>
+      <c r="I55">
+        <v>520</v>
+      </c>
+      <c r="J55">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56">
+        <v>510</v>
+      </c>
+      <c r="C56">
+        <v>212</v>
+      </c>
+      <c r="D56">
+        <v>4484</v>
+      </c>
+      <c r="E56">
+        <v>20</v>
+      </c>
+      <c r="F56">
+        <v>121</v>
+      </c>
+      <c r="G56">
+        <v>61</v>
+      </c>
+      <c r="H56">
+        <v>96</v>
+      </c>
+      <c r="I56">
+        <v>475</v>
+      </c>
+      <c r="J56">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>272</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>232</v>
+      </c>
+      <c r="D57">
+        <v>300</v>
+      </c>
+      <c r="E57">
+        <v>5536</v>
+      </c>
+      <c r="F57">
+        <v>23</v>
+      </c>
+      <c r="G57">
+        <v>155</v>
+      </c>
+      <c r="H57">
+        <v>73</v>
+      </c>
+      <c r="I57">
+        <v>69</v>
+      </c>
+      <c r="J57">
+        <v>359</v>
+      </c>
+      <c r="K57">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>272</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>188</v>
+      </c>
+      <c r="D58">
+        <v>282</v>
+      </c>
+      <c r="E58">
+        <v>5404</v>
+      </c>
+      <c r="F58">
+        <v>21</v>
+      </c>
+      <c r="G58">
+        <v>154</v>
+      </c>
+      <c r="H58">
+        <v>76</v>
+      </c>
+      <c r="I58">
+        <v>69</v>
+      </c>
+      <c r="J58">
+        <v>326</v>
+      </c>
+      <c r="K58">
         <v>31</v>
       </c>
-      <c r="AD17">
-        <v>1294</v>
-      </c>
-      <c r="AE17">
-        <v>374</v>
-      </c>
-      <c r="AF17">
-        <v>7191</v>
-      </c>
-      <c r="AG17">
-        <v>25</v>
-      </c>
-      <c r="AH17">
-        <v>98</v>
-      </c>
-      <c r="AI17">
-        <v>114</v>
-      </c>
-      <c r="AJ17">
-        <v>108</v>
-      </c>
-      <c r="AK17">
-        <v>304</v>
-      </c>
-      <c r="AL17">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC18" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD18">
-        <v>1125</v>
-      </c>
-      <c r="AE18">
-        <v>432</v>
-      </c>
-      <c r="AF18">
-        <v>7276</v>
-      </c>
-      <c r="AG18">
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>272</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>223</v>
+      </c>
+      <c r="D59">
+        <v>305</v>
+      </c>
+      <c r="E59">
+        <v>5261</v>
+      </c>
+      <c r="F59">
+        <v>23</v>
+      </c>
+      <c r="G59">
+        <v>163</v>
+      </c>
+      <c r="H59">
+        <v>77</v>
+      </c>
+      <c r="I59">
+        <v>63</v>
+      </c>
+      <c r="J59">
+        <v>280</v>
+      </c>
+      <c r="K59">
         <v>32</v>
       </c>
-      <c r="AH18">
-        <v>99</v>
-      </c>
-      <c r="AI18">
-        <v>110</v>
-      </c>
-      <c r="AJ18">
-        <v>121</v>
-      </c>
-      <c r="AK18">
-        <v>358</v>
-      </c>
-      <c r="AL18">
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>272</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>231</v>
+      </c>
+      <c r="D60">
+        <v>291</v>
+      </c>
+      <c r="E60">
+        <v>4768</v>
+      </c>
+      <c r="F60">
+        <v>22</v>
+      </c>
+      <c r="G60">
+        <v>156</v>
+      </c>
+      <c r="H60">
+        <v>65</v>
+      </c>
+      <c r="I60">
+        <v>62</v>
+      </c>
+      <c r="J60">
+        <v>420</v>
+      </c>
+      <c r="K60">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>231</v>
+      </c>
+      <c r="D61">
+        <v>326</v>
+      </c>
+      <c r="E61">
+        <v>5187</v>
+      </c>
+      <c r="F61">
+        <v>22</v>
+      </c>
+      <c r="G61">
+        <v>172</v>
+      </c>
+      <c r="H61">
+        <v>73</v>
+      </c>
+      <c r="I61">
+        <v>68</v>
+      </c>
+      <c r="J61">
+        <v>305</v>
+      </c>
+      <c r="K61">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>272</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>229</v>
+      </c>
+      <c r="D62">
+        <v>308</v>
+      </c>
+      <c r="E62">
+        <v>5456</v>
+      </c>
+      <c r="F62">
+        <v>22</v>
+      </c>
+      <c r="G62">
+        <v>168</v>
+      </c>
+      <c r="H62">
+        <v>75</v>
+      </c>
+      <c r="I62">
+        <v>74</v>
+      </c>
+      <c r="J62">
+        <v>351</v>
+      </c>
+      <c r="K62">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>272</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>170</v>
+      </c>
+      <c r="D63">
+        <v>340</v>
+      </c>
+      <c r="E63">
+        <v>5483</v>
+      </c>
+      <c r="F63">
+        <v>20</v>
+      </c>
+      <c r="G63">
+        <v>173</v>
+      </c>
+      <c r="H63">
+        <v>64</v>
+      </c>
+      <c r="I63">
+        <v>67</v>
+      </c>
+      <c r="J63">
+        <v>307</v>
+      </c>
+      <c r="K63">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>272</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>1701</v>
+      </c>
+      <c r="D64">
+        <v>421</v>
+      </c>
+      <c r="E64">
+        <v>11</v>
+      </c>
+      <c r="F64">
+        <v>671</v>
+      </c>
+      <c r="G64">
+        <v>46</v>
+      </c>
+      <c r="H64">
+        <v>174</v>
+      </c>
+      <c r="I64">
+        <v>71</v>
+      </c>
+      <c r="J64">
+        <v>128</v>
+      </c>
+      <c r="K64">
+        <v>367</v>
+      </c>
+      <c r="L64">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>272</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>364</v>
+      </c>
+      <c r="D65">
+        <v>258</v>
+      </c>
+      <c r="E65">
+        <v>7335</v>
+      </c>
+      <c r="F65">
+        <v>46</v>
+      </c>
+      <c r="G65">
+        <v>185</v>
+      </c>
+      <c r="H65">
+        <v>75</v>
+      </c>
+      <c r="I65">
+        <v>122</v>
+      </c>
+      <c r="J65">
+        <v>408</v>
+      </c>
+      <c r="K65">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>272</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66">
+        <v>682</v>
+      </c>
+      <c r="D66">
+        <v>300</v>
+      </c>
+      <c r="E66">
+        <v>7315</v>
+      </c>
+      <c r="F66">
+        <v>32</v>
+      </c>
+      <c r="G66">
+        <v>164</v>
+      </c>
+      <c r="H66">
+        <v>70</v>
+      </c>
+      <c r="I66">
+        <v>129</v>
+      </c>
+      <c r="J66">
+        <v>416</v>
+      </c>
+      <c r="K66">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>272</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67">
+        <v>327</v>
+      </c>
+      <c r="D67">
+        <v>289</v>
+      </c>
+      <c r="E67">
+        <v>7512</v>
+      </c>
+      <c r="F67">
+        <v>37</v>
+      </c>
+      <c r="G67">
+        <v>181</v>
+      </c>
+      <c r="H67">
+        <v>71</v>
+      </c>
+      <c r="I67">
+        <v>126</v>
+      </c>
+      <c r="J67">
+        <v>459</v>
+      </c>
+      <c r="K67">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>272</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68">
+        <v>326</v>
+      </c>
+      <c r="D68">
+        <v>286</v>
+      </c>
+      <c r="E68">
+        <v>7052</v>
+      </c>
+      <c r="F68">
+        <v>35</v>
+      </c>
+      <c r="G68">
+        <v>165</v>
+      </c>
+      <c r="H68">
+        <v>72</v>
+      </c>
+      <c r="I68">
+        <v>118</v>
+      </c>
+      <c r="J68">
+        <v>407</v>
+      </c>
+      <c r="K68">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>272</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>331</v>
+      </c>
+      <c r="D69">
+        <v>296</v>
+      </c>
+      <c r="E69">
+        <v>7108</v>
+      </c>
+      <c r="F69">
+        <v>36</v>
+      </c>
+      <c r="G69">
+        <v>173</v>
+      </c>
+      <c r="H69">
+        <v>72</v>
+      </c>
+      <c r="I69">
+        <v>123</v>
+      </c>
+      <c r="J69">
+        <v>461</v>
+      </c>
+      <c r="K69">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>272</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70">
+        <v>2356</v>
+      </c>
+      <c r="D70">
+        <v>278</v>
+      </c>
+      <c r="E70">
+        <v>12</v>
+      </c>
+      <c r="F70">
+        <v>551</v>
+      </c>
+      <c r="G70">
+        <v>43</v>
+      </c>
+      <c r="H70">
+        <v>176</v>
+      </c>
+      <c r="I70">
+        <v>73</v>
+      </c>
+      <c r="J70">
+        <v>128</v>
+      </c>
+      <c r="K70">
+        <v>385</v>
+      </c>
+      <c r="L70">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>272</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71">
+        <v>2032</v>
+      </c>
+      <c r="D71">
+        <v>292</v>
+      </c>
+      <c r="E71">
+        <v>11</v>
+      </c>
+      <c r="F71">
+        <v>361</v>
+      </c>
+      <c r="G71">
+        <v>38</v>
+      </c>
+      <c r="H71">
+        <v>174</v>
+      </c>
+      <c r="I71">
+        <v>74</v>
+      </c>
+      <c r="J71">
+        <v>133</v>
+      </c>
+      <c r="K71">
+        <v>572</v>
+      </c>
+      <c r="L71">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72">
+        <v>439</v>
+      </c>
+      <c r="C72">
+        <v>509</v>
+      </c>
+      <c r="D72">
+        <v>4206</v>
+      </c>
+      <c r="E72">
+        <v>24</v>
+      </c>
+      <c r="F72">
+        <v>367</v>
+      </c>
+      <c r="G72">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC19" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD19">
-        <v>1149</v>
-      </c>
-      <c r="AE19">
-        <v>374</v>
-      </c>
-      <c r="AF19">
-        <v>6873</v>
-      </c>
-      <c r="AG19">
-        <v>32</v>
-      </c>
-      <c r="AH19">
-        <v>96</v>
-      </c>
-      <c r="AI19">
-        <v>114</v>
-      </c>
-      <c r="AJ19">
-        <v>115</v>
-      </c>
-      <c r="AK19">
-        <v>315</v>
-      </c>
-      <c r="AL19">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC20" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD20">
-        <v>1163</v>
-      </c>
-      <c r="AE20">
-        <v>384</v>
-      </c>
-      <c r="AF20">
-        <v>7056</v>
-      </c>
-      <c r="AG20">
-        <v>27</v>
-      </c>
-      <c r="AH20">
-        <v>98</v>
-      </c>
-      <c r="AI20">
-        <v>111</v>
-      </c>
-      <c r="AJ20">
-        <v>119</v>
-      </c>
-      <c r="AK20">
-        <v>323</v>
-      </c>
-      <c r="AL20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC21" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD21">
-        <v>1206</v>
-      </c>
-      <c r="AE21">
-        <v>412</v>
-      </c>
-      <c r="AF21">
-        <v>7218</v>
-      </c>
-      <c r="AG21">
-        <v>22</v>
-      </c>
-      <c r="AH21">
-        <v>103</v>
-      </c>
-      <c r="AI21">
-        <v>114</v>
-      </c>
-      <c r="AJ21">
-        <v>121</v>
-      </c>
-      <c r="AK21">
-        <v>365</v>
-      </c>
-      <c r="AL21">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC22" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD22">
-        <v>776</v>
-      </c>
-      <c r="AE22">
-        <v>251</v>
-      </c>
-      <c r="AF22">
-        <v>5111</v>
-      </c>
-      <c r="AG22">
-        <v>18</v>
-      </c>
-      <c r="AH22">
-        <v>122</v>
-      </c>
-      <c r="AI22">
-        <v>62</v>
-      </c>
-      <c r="AJ22">
-        <v>99</v>
-      </c>
-      <c r="AK22">
-        <v>509</v>
-      </c>
-      <c r="AL22">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC23" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD23">
-        <v>674</v>
-      </c>
-      <c r="AE23">
-        <v>257</v>
-      </c>
-      <c r="AF23">
-        <v>4552</v>
-      </c>
-      <c r="AG23">
-        <v>21</v>
-      </c>
-      <c r="AH23">
-        <v>124</v>
-      </c>
-      <c r="AI23">
-        <v>60</v>
-      </c>
-      <c r="AJ23">
-        <v>94</v>
-      </c>
-      <c r="AK23">
-        <v>552</v>
-      </c>
-      <c r="AL23">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC24" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD24">
-        <v>560</v>
-      </c>
-      <c r="AE24">
-        <v>219</v>
-      </c>
-      <c r="AF24">
-        <v>4221</v>
-      </c>
-      <c r="AG24">
-        <v>17</v>
-      </c>
-      <c r="AH24">
-        <v>118</v>
-      </c>
-      <c r="AI24">
-        <v>66</v>
-      </c>
-      <c r="AJ24">
-        <v>97</v>
-      </c>
-      <c r="AK24">
-        <v>420</v>
-      </c>
-      <c r="AL24">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC25" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD25">
-        <v>544</v>
-      </c>
-      <c r="AE25">
-        <v>239</v>
-      </c>
-      <c r="AF25">
-        <v>4513</v>
-      </c>
-      <c r="AG25">
-        <v>18</v>
-      </c>
-      <c r="AH25">
-        <v>122</v>
-      </c>
-      <c r="AI25">
-        <v>64</v>
-      </c>
-      <c r="AJ25">
-        <v>95</v>
-      </c>
-      <c r="AK25">
-        <v>520</v>
-      </c>
-      <c r="AL25">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC26" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD26">
-        <v>510</v>
-      </c>
-      <c r="AE26">
-        <v>212</v>
-      </c>
-      <c r="AF26">
-        <v>4484</v>
-      </c>
-      <c r="AG26">
-        <v>20</v>
-      </c>
-      <c r="AH26">
-        <v>121</v>
-      </c>
-      <c r="AI26">
-        <v>61</v>
-      </c>
-      <c r="AJ26">
-        <v>96</v>
-      </c>
-      <c r="AK26">
-        <v>475</v>
-      </c>
-      <c r="AL26">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC27" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD27">
-        <v>232</v>
-      </c>
-      <c r="AE27">
-        <v>300</v>
-      </c>
-      <c r="AF27">
-        <v>5536</v>
-      </c>
-      <c r="AG27">
-        <v>23</v>
-      </c>
-      <c r="AH27">
-        <v>155</v>
-      </c>
-      <c r="AI27">
-        <v>73</v>
-      </c>
-      <c r="AJ27">
-        <v>69</v>
-      </c>
-      <c r="AK27">
-        <v>359</v>
-      </c>
-      <c r="AL27">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC28" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD28">
-        <v>188</v>
-      </c>
-      <c r="AE28">
-        <v>282</v>
-      </c>
-      <c r="AF28">
-        <v>5404</v>
-      </c>
-      <c r="AG28">
-        <v>21</v>
-      </c>
-      <c r="AH28">
-        <v>154</v>
-      </c>
-      <c r="AI28">
-        <v>76</v>
-      </c>
-      <c r="AJ28">
-        <v>69</v>
-      </c>
-      <c r="AK28">
-        <v>326</v>
-      </c>
-      <c r="AL28">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC29" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD29">
-        <v>223</v>
-      </c>
-      <c r="AE29">
-        <v>305</v>
-      </c>
-      <c r="AF29">
-        <v>5261</v>
-      </c>
-      <c r="AG29">
-        <v>23</v>
-      </c>
-      <c r="AH29">
-        <v>163</v>
-      </c>
-      <c r="AI29">
-        <v>77</v>
-      </c>
-      <c r="AJ29">
-        <v>63</v>
-      </c>
-      <c r="AK29">
-        <v>280</v>
-      </c>
-      <c r="AL29">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC30" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD30">
-        <v>231</v>
-      </c>
-      <c r="AE30">
-        <v>291</v>
-      </c>
-      <c r="AF30">
-        <v>4768</v>
-      </c>
-      <c r="AG30">
-        <v>22</v>
-      </c>
-      <c r="AH30">
-        <v>156</v>
-      </c>
-      <c r="AI30">
-        <v>65</v>
-      </c>
-      <c r="AJ30">
-        <v>62</v>
-      </c>
-      <c r="AK30">
-        <v>420</v>
-      </c>
-      <c r="AL30">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC31" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD31">
-        <v>231</v>
-      </c>
-      <c r="AE31">
-        <v>326</v>
-      </c>
-      <c r="AF31">
-        <v>5187</v>
-      </c>
-      <c r="AG31">
-        <v>22</v>
-      </c>
-      <c r="AH31">
-        <v>172</v>
-      </c>
-      <c r="AI31">
-        <v>73</v>
-      </c>
-      <c r="AJ31">
-        <v>68</v>
-      </c>
-      <c r="AK31">
-        <v>305</v>
-      </c>
-      <c r="AL31">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC32" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD32">
-        <v>229</v>
-      </c>
-      <c r="AE32">
-        <v>308</v>
-      </c>
-      <c r="AF32">
-        <v>5456</v>
-      </c>
-      <c r="AG32">
-        <v>22</v>
-      </c>
-      <c r="AH32">
-        <v>168</v>
-      </c>
-      <c r="AI32">
-        <v>75</v>
-      </c>
-      <c r="AJ32">
-        <v>74</v>
-      </c>
-      <c r="AK32">
-        <v>351</v>
-      </c>
-      <c r="AL32">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC33" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD33">
-        <v>170</v>
-      </c>
-      <c r="AE33">
-        <v>340</v>
-      </c>
-      <c r="AF33">
-        <v>5483</v>
-      </c>
-      <c r="AG33">
-        <v>20</v>
-      </c>
-      <c r="AH33">
-        <v>173</v>
-      </c>
-      <c r="AI33">
-        <v>64</v>
-      </c>
-      <c r="AJ33">
-        <v>67</v>
-      </c>
-      <c r="AK33">
-        <v>307</v>
-      </c>
-      <c r="AL33">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC34" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD34">
-        <v>1701</v>
-      </c>
-      <c r="AE34">
-        <v>421</v>
-      </c>
-      <c r="AF34">
-        <v>11671</v>
-      </c>
-      <c r="AG34">
-        <v>46</v>
-      </c>
-      <c r="AH34">
-        <v>174</v>
-      </c>
-      <c r="AI34">
-        <v>71</v>
-      </c>
-      <c r="AJ34">
+      <c r="H72">
         <v>128</v>
       </c>
-      <c r="AK34">
-        <v>367</v>
-      </c>
-      <c r="AL34">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC35" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD35">
-        <v>364</v>
-      </c>
-      <c r="AE35">
-        <v>258</v>
-      </c>
-      <c r="AF35">
-        <v>7335</v>
-      </c>
-      <c r="AG35">
-        <v>46</v>
-      </c>
-      <c r="AH35">
-        <v>185</v>
-      </c>
-      <c r="AI35">
-        <v>75</v>
-      </c>
-      <c r="AJ35">
-        <v>122</v>
-      </c>
-      <c r="AK35">
-        <v>408</v>
-      </c>
-      <c r="AL35">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC36" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD36">
-        <v>682</v>
-      </c>
-      <c r="AE36">
-        <v>300</v>
-      </c>
-      <c r="AF36">
-        <v>7315</v>
-      </c>
-      <c r="AG36">
-        <v>32</v>
-      </c>
-      <c r="AH36">
-        <v>164</v>
-      </c>
-      <c r="AI36">
-        <v>70</v>
-      </c>
-      <c r="AJ36">
-        <v>129</v>
-      </c>
-      <c r="AK36">
-        <v>416</v>
-      </c>
-      <c r="AL36">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC37" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD37">
-        <v>327</v>
-      </c>
-      <c r="AE37">
-        <v>289</v>
-      </c>
-      <c r="AF37">
-        <v>7512</v>
-      </c>
-      <c r="AG37">
-        <v>37</v>
-      </c>
-      <c r="AH37">
-        <v>181</v>
-      </c>
-      <c r="AI37">
-        <v>71</v>
-      </c>
-      <c r="AJ37">
-        <v>126</v>
-      </c>
-      <c r="AK37">
-        <v>459</v>
-      </c>
-      <c r="AL37">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC38" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD38">
-        <v>326</v>
-      </c>
-      <c r="AE38">
-        <v>286</v>
-      </c>
-      <c r="AF38">
-        <v>7052</v>
-      </c>
-      <c r="AG38">
-        <v>35</v>
-      </c>
-      <c r="AH38">
-        <v>165</v>
-      </c>
-      <c r="AI38">
-        <v>72</v>
-      </c>
-      <c r="AJ38">
-        <v>118</v>
-      </c>
-      <c r="AK38">
-        <v>407</v>
-      </c>
-      <c r="AL38">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC39" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD39">
-        <v>331</v>
-      </c>
-      <c r="AE39">
-        <v>296</v>
-      </c>
-      <c r="AF39">
-        <v>7108</v>
-      </c>
-      <c r="AG39">
-        <v>36</v>
-      </c>
-      <c r="AH39">
-        <v>173</v>
-      </c>
-      <c r="AI39">
-        <v>72</v>
-      </c>
-      <c r="AJ39">
-        <v>123</v>
-      </c>
-      <c r="AK39">
-        <v>461</v>
-      </c>
-      <c r="AL39">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC40" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD40">
-        <v>2356</v>
-      </c>
-      <c r="AE40">
-        <v>278</v>
-      </c>
-      <c r="AF40">
-        <v>12551</v>
-      </c>
-      <c r="AG40">
-        <v>43</v>
-      </c>
-      <c r="AH40">
-        <v>176</v>
-      </c>
-      <c r="AI40">
-        <v>73</v>
-      </c>
-      <c r="AJ40">
-        <v>128</v>
-      </c>
-      <c r="AK40">
-        <v>385</v>
-      </c>
-      <c r="AL40">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC41" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD41">
-        <v>2032</v>
-      </c>
-      <c r="AE41">
-        <v>292</v>
-      </c>
-      <c r="AF41">
-        <v>11361</v>
-      </c>
-      <c r="AG41">
-        <v>38</v>
-      </c>
-      <c r="AH41">
-        <v>174</v>
-      </c>
-      <c r="AI41">
-        <v>74</v>
-      </c>
-      <c r="AJ41">
-        <v>133</v>
-      </c>
-      <c r="AK41">
-        <v>572</v>
-      </c>
-      <c r="AL41">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="29:38" x14ac:dyDescent="0.25">
-      <c r="AC42" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD42">
-        <v>439</v>
-      </c>
-      <c r="AE42">
-        <v>509</v>
-      </c>
-      <c r="AF42">
-        <v>4206</v>
-      </c>
-      <c r="AG42">
-        <v>24</v>
-      </c>
-      <c r="AH42">
-        <v>367</v>
-      </c>
-      <c r="AI42">
-        <v>10</v>
-      </c>
-      <c r="AJ42">
-        <v>128</v>
-      </c>
-      <c r="AK42">
+      <c r="I72">
         <v>153</v>
       </c>
-      <c r="AL42">
+      <c r="J72">
         <v>57</v>
       </c>
     </row>
@@ -7609,57 +7960,57 @@
         <v>27</v>
       </c>
       <c r="B1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" t="s">
         <v>165</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>166</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>167</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>168</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>169</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>170</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>171</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>172</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>173</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
         <v>174</v>
       </c>
-      <c r="L1" t="s">
-        <v>175</v>
-      </c>
-      <c r="M1" t="s">
-        <v>176</v>
-      </c>
-      <c r="N1" t="s">
-        <v>177</v>
-      </c>
-      <c r="O1" t="s">
-        <v>178</v>
-      </c>
-      <c r="P1" t="s">
-        <v>179</v>
-      </c>
       <c r="Q1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B2" s="3">
         <v>344</v>
@@ -7712,7 +8063,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B3" s="3">
         <v>696.80919931856897</v>
@@ -7818,7 +8169,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B5" s="3">
         <v>719.19277108433732</v>
@@ -7871,7 +8222,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B6" s="3">
         <v>698</v>
@@ -7950,48 +8301,48 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
         <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D1" t="s">
         <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F1" t="s">
         <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H1" t="s">
         <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J1" t="s">
         <v>22</v>
       </c>
       <c r="K1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="L1" t="s">
         <v>20</v>
       </c>
       <c r="M1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -8283,7 +8634,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B10">
         <v>87</v>
@@ -8306,7 +8657,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -8329,7 +8680,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B12">
         <v>0.01</v>
@@ -8352,7 +8703,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -8378,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I14">
         <v>5</v>
@@ -8419,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -8460,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -8501,7 +8852,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -8542,7 +8893,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -8583,7 +8934,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -8624,7 +8975,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -8644,7 +8995,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B21">
         <v>55</v>
@@ -8656,7 +9007,7 @@
         <v>10</v>
       </c>
       <c r="H21" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J21">
         <v>80</v>
@@ -8667,7 +9018,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -8679,7 +9030,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J22">
         <v>8</v>
@@ -8690,7 +9041,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B23">
         <v>0.03</v>
@@ -8702,7 +9053,7 @@
         <v>0.06</v>
       </c>
       <c r="H23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J23">
         <v>0.1</v>
@@ -8713,48 +9064,48 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
       </c>
       <c r="G26" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H26" t="s">
         <v>23</v>
       </c>
       <c r="I26" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J26" t="s">
         <v>22</v>
       </c>
       <c r="K26" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="L26" t="s">
         <v>20</v>
       </c>
       <c r="M26" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -9046,7 +9397,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B35">
         <v>260</v>
@@ -9069,7 +9420,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B36">
         <v>25</v>
@@ -9092,7 +9443,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B37">
         <v>0.09</v>
@@ -9115,7 +9466,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -9407,7 +9758,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B46">
         <v>200</v>
@@ -9430,7 +9781,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B47">
         <v>18</v>
@@ -9453,7 +9804,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B48">
         <v>0.09</v>
@@ -9476,7 +9827,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -9768,7 +10119,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B57">
         <v>443</v>
@@ -9791,7 +10142,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B58">
         <v>47</v>
@@ -9814,7 +10165,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B59">
         <v>0.11</v>
@@ -9837,7 +10188,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -10129,7 +10480,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B68">
         <v>262</v>
@@ -10152,7 +10503,7 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B69">
         <v>11</v>
@@ -10175,7 +10526,7 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B70">
         <v>0.04</v>
@@ -10214,16 +10565,16 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>20</v>
@@ -10238,7 +10589,7 @@
         <v>23</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>28</v>
@@ -10247,48 +10598,48 @@
         <v>25</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B2">
         <v>112</v>
@@ -10434,7 +10785,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B4">
         <v>72</v>
@@ -10508,7 +10859,7 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B5">
         <v>91</v>
@@ -10609,13 +10960,13 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
@@ -10637,10 +10988,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -10675,10 +11026,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I3">
         <v>209</v>
@@ -10695,10 +11046,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C4">
         <v>25</v>
@@ -10718,10 +11069,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5">
         <v>78</v>
@@ -10750,10 +11101,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -10788,10 +11139,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C7">
         <v>21</v>
@@ -10826,10 +11177,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C8">
         <v>24</v>
@@ -10864,10 +11215,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E9">
         <v>71</v>
@@ -10896,10 +11247,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -10919,10 +11270,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>73</v>
@@ -10936,10 +11287,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -10956,10 +11307,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C13">
         <v>22</v>
@@ -10988,10 +11339,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B14" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C14">
         <v>32</v>
@@ -11026,10 +11377,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B15" t="s">
         <v>247</v>
-      </c>
-      <c r="B15" t="s">
-        <v>252</v>
       </c>
       <c r="K15">
         <v>4890</v>
@@ -11040,10 +11391,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B16" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C16">
         <v>25</v>
@@ -11078,7 +11429,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C17">
         <v>24</v>
@@ -11113,10 +11464,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -11179,16 +11530,16 @@
         <v>27</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>20</v>
@@ -11209,16 +11560,16 @@
         <v>25</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>19</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="P1" s="6" t="s">
         <v>24</v>
@@ -11226,7 +11577,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3">
         <v>69730.088382769696</v>
@@ -11276,7 +11627,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3">
         <v>78205.685843357511</v>
@@ -11324,7 +11675,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3">
         <v>76322.601314211002</v>
@@ -11374,7 +11725,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3">
         <v>73873.61096552349</v>
@@ -11422,7 +11773,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3">
         <v>71368.763553211669</v>
@@ -11470,7 +11821,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B7" s="3">
         <v>70803</v>
@@ -11514,7 +11865,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B8" s="3">
         <v>70762.744698607727</v>
@@ -11560,7 +11911,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B9" s="3">
         <v>70813.074433537258</v>
@@ -11610,7 +11961,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B10" s="4">
         <v>70019.527635382707</v>
@@ -11660,7 +12011,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B11" s="3">
         <v>73045.390387519874</v>
@@ -11710,7 +12061,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B12" s="3">
         <v>77119.838236414682</v>

--- a/data/article_tables/data1.xlsx
+++ b/data/article_tables/data1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492F120B-1C20-4B56-B58A-CC62FCC80D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECF83D9-6B67-4165-A588-8B0B40CB0EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="697" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="697" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicative Elements" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="275">
   <si>
     <t>Method</t>
   </si>
@@ -940,9 +940,6 @@
   </si>
   <si>
     <t>Sr (ppm)</t>
-  </si>
-  <si>
-    <t>Carpathian</t>
   </si>
   <si>
     <t>Göllü Dag</t>
@@ -5919,7 +5916,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -6201,15 +6198,15 @@
         <v>61</v>
       </c>
       <c r="I20" t="s">
+        <v>273</v>
+      </c>
+      <c r="J20" t="s">
         <v>274</v>
-      </c>
-      <c r="J20" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B21">
         <v>298</v>
@@ -6241,7 +6238,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B22">
         <v>312</v>
@@ -6273,7 +6270,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B23">
         <v>229</v>
@@ -6305,7 +6302,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B24">
         <v>307</v>
@@ -6337,7 +6334,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B25">
         <v>237</v>
@@ -6369,7 +6366,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B26">
         <v>417</v>
@@ -6401,7 +6398,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B27">
         <v>573</v>
@@ -7103,7 +7100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -7135,7 +7132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>73</v>
       </c>
@@ -7167,7 +7164,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>73</v>
       </c>
@@ -7199,7 +7196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>29</v>
       </c>
@@ -7231,7 +7228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -7263,7 +7260,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -7295,7 +7292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>29</v>
       </c>
@@ -7327,7 +7324,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -7359,541 +7356,487 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="C57">
-        <v>232</v>
+        <v>300</v>
       </c>
       <c r="D57">
+        <v>5536</v>
+      </c>
+      <c r="E57">
+        <v>23</v>
+      </c>
+      <c r="F57">
+        <v>155</v>
+      </c>
+      <c r="G57">
+        <v>73</v>
+      </c>
+      <c r="H57">
+        <v>69</v>
+      </c>
+      <c r="I57">
+        <v>359</v>
+      </c>
+      <c r="J57">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58">
+        <v>188</v>
+      </c>
+      <c r="C58">
+        <v>282</v>
+      </c>
+      <c r="D58">
+        <v>5404</v>
+      </c>
+      <c r="E58">
+        <v>21</v>
+      </c>
+      <c r="F58">
+        <v>154</v>
+      </c>
+      <c r="G58">
+        <v>76</v>
+      </c>
+      <c r="H58">
+        <v>69</v>
+      </c>
+      <c r="I58">
+        <v>326</v>
+      </c>
+      <c r="J58">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59">
+        <v>223</v>
+      </c>
+      <c r="C59">
+        <v>305</v>
+      </c>
+      <c r="D59">
+        <v>5261</v>
+      </c>
+      <c r="E59">
+        <v>23</v>
+      </c>
+      <c r="F59">
+        <v>163</v>
+      </c>
+      <c r="G59">
+        <v>77</v>
+      </c>
+      <c r="H59">
+        <v>63</v>
+      </c>
+      <c r="I59">
+        <v>280</v>
+      </c>
+      <c r="J59">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60">
+        <v>231</v>
+      </c>
+      <c r="C60">
+        <v>291</v>
+      </c>
+      <c r="D60">
+        <v>4768</v>
+      </c>
+      <c r="E60">
+        <v>22</v>
+      </c>
+      <c r="F60">
+        <v>156</v>
+      </c>
+      <c r="G60">
+        <v>65</v>
+      </c>
+      <c r="H60">
+        <v>62</v>
+      </c>
+      <c r="I60">
+        <v>420</v>
+      </c>
+      <c r="J60">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61">
+        <v>231</v>
+      </c>
+      <c r="C61">
+        <v>326</v>
+      </c>
+      <c r="D61">
+        <v>5187</v>
+      </c>
+      <c r="E61">
+        <v>22</v>
+      </c>
+      <c r="F61">
+        <v>172</v>
+      </c>
+      <c r="G61">
+        <v>73</v>
+      </c>
+      <c r="H61">
+        <v>68</v>
+      </c>
+      <c r="I61">
+        <v>305</v>
+      </c>
+      <c r="J61">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62">
+        <v>229</v>
+      </c>
+      <c r="C62">
+        <v>308</v>
+      </c>
+      <c r="D62">
+        <v>5456</v>
+      </c>
+      <c r="E62">
+        <v>22</v>
+      </c>
+      <c r="F62">
+        <v>168</v>
+      </c>
+      <c r="G62">
+        <v>75</v>
+      </c>
+      <c r="H62">
+        <v>74</v>
+      </c>
+      <c r="I62">
+        <v>351</v>
+      </c>
+      <c r="J62">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63">
+        <v>170</v>
+      </c>
+      <c r="C63">
+        <v>340</v>
+      </c>
+      <c r="D63">
+        <v>5483</v>
+      </c>
+      <c r="E63">
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <v>173</v>
+      </c>
+      <c r="G63">
+        <v>64</v>
+      </c>
+      <c r="H63">
+        <v>67</v>
+      </c>
+      <c r="I63">
+        <v>307</v>
+      </c>
+      <c r="J63">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64">
+        <v>1701</v>
+      </c>
+      <c r="C64">
+        <v>421</v>
+      </c>
+      <c r="D64">
+        <v>11671</v>
+      </c>
+      <c r="E64">
+        <v>46</v>
+      </c>
+      <c r="F64">
+        <v>174</v>
+      </c>
+      <c r="G64">
+        <v>71</v>
+      </c>
+      <c r="H64">
+        <v>128</v>
+      </c>
+      <c r="I64">
+        <v>367</v>
+      </c>
+      <c r="J64">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65">
+        <v>364</v>
+      </c>
+      <c r="C65">
+        <v>258</v>
+      </c>
+      <c r="D65">
+        <v>7335</v>
+      </c>
+      <c r="E65">
+        <v>46</v>
+      </c>
+      <c r="F65">
+        <v>185</v>
+      </c>
+      <c r="G65">
+        <v>75</v>
+      </c>
+      <c r="H65">
+        <v>122</v>
+      </c>
+      <c r="I65">
+        <v>408</v>
+      </c>
+      <c r="J65">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66">
+        <v>682</v>
+      </c>
+      <c r="C66">
         <v>300</v>
       </c>
-      <c r="E57">
-        <v>5536</v>
-      </c>
-      <c r="F57">
-        <v>23</v>
-      </c>
-      <c r="G57">
-        <v>155</v>
-      </c>
-      <c r="H57">
+      <c r="D66">
+        <v>7315</v>
+      </c>
+      <c r="E66">
+        <v>32</v>
+      </c>
+      <c r="F66">
+        <v>164</v>
+      </c>
+      <c r="G66">
+        <v>70</v>
+      </c>
+      <c r="H66">
+        <v>129</v>
+      </c>
+      <c r="I66">
+        <v>416</v>
+      </c>
+      <c r="J66">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67">
+        <v>327</v>
+      </c>
+      <c r="C67">
+        <v>289</v>
+      </c>
+      <c r="D67">
+        <v>7512</v>
+      </c>
+      <c r="E67">
+        <v>37</v>
+      </c>
+      <c r="F67">
+        <v>181</v>
+      </c>
+      <c r="G67">
+        <v>71</v>
+      </c>
+      <c r="H67">
+        <v>126</v>
+      </c>
+      <c r="I67">
+        <v>459</v>
+      </c>
+      <c r="J67">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68">
+        <v>326</v>
+      </c>
+      <c r="C68">
+        <v>286</v>
+      </c>
+      <c r="D68">
+        <v>7052</v>
+      </c>
+      <c r="E68">
+        <v>35</v>
+      </c>
+      <c r="F68">
+        <v>165</v>
+      </c>
+      <c r="G68">
+        <v>72</v>
+      </c>
+      <c r="H68">
+        <v>118</v>
+      </c>
+      <c r="I68">
+        <v>407</v>
+      </c>
+      <c r="J68">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>331</v>
+      </c>
+      <c r="C69">
+        <v>296</v>
+      </c>
+      <c r="D69">
+        <v>7108</v>
+      </c>
+      <c r="E69">
+        <v>36</v>
+      </c>
+      <c r="F69">
+        <v>173</v>
+      </c>
+      <c r="G69">
+        <v>72</v>
+      </c>
+      <c r="H69">
+        <v>123</v>
+      </c>
+      <c r="I69">
+        <v>461</v>
+      </c>
+      <c r="J69">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70">
+        <v>2356</v>
+      </c>
+      <c r="C70">
+        <v>278</v>
+      </c>
+      <c r="D70">
+        <v>12551</v>
+      </c>
+      <c r="E70">
+        <v>43</v>
+      </c>
+      <c r="F70">
+        <v>176</v>
+      </c>
+      <c r="G70">
         <v>73</v>
       </c>
-      <c r="I57">
-        <v>69</v>
-      </c>
-      <c r="J57">
-        <v>359</v>
-      </c>
-      <c r="K57">
+      <c r="H70">
+        <v>128</v>
+      </c>
+      <c r="I70">
+        <v>385</v>
+      </c>
+      <c r="J70">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>2032</v>
+      </c>
+      <c r="C71">
+        <v>292</v>
+      </c>
+      <c r="D71">
+        <v>11361</v>
+      </c>
+      <c r="E71">
+        <v>38</v>
+      </c>
+      <c r="F71">
+        <v>174</v>
+      </c>
+      <c r="G71">
+        <v>74</v>
+      </c>
+      <c r="H71">
+        <v>133</v>
+      </c>
+      <c r="I71">
+        <v>572</v>
+      </c>
+      <c r="J71">
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>272</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58">
-        <v>188</v>
-      </c>
-      <c r="D58">
-        <v>282</v>
-      </c>
-      <c r="E58">
-        <v>5404</v>
-      </c>
-      <c r="F58">
-        <v>21</v>
-      </c>
-      <c r="G58">
-        <v>154</v>
-      </c>
-      <c r="H58">
-        <v>76</v>
-      </c>
-      <c r="I58">
-        <v>69</v>
-      </c>
-      <c r="J58">
-        <v>326</v>
-      </c>
-      <c r="K58">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>272</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59">
-        <v>223</v>
-      </c>
-      <c r="D59">
-        <v>305</v>
-      </c>
-      <c r="E59">
-        <v>5261</v>
-      </c>
-      <c r="F59">
-        <v>23</v>
-      </c>
-      <c r="G59">
-        <v>163</v>
-      </c>
-      <c r="H59">
-        <v>77</v>
-      </c>
-      <c r="I59">
-        <v>63</v>
-      </c>
-      <c r="J59">
-        <v>280</v>
-      </c>
-      <c r="K59">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>272</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60">
-        <v>231</v>
-      </c>
-      <c r="D60">
-        <v>291</v>
-      </c>
-      <c r="E60">
-        <v>4768</v>
-      </c>
-      <c r="F60">
-        <v>22</v>
-      </c>
-      <c r="G60">
-        <v>156</v>
-      </c>
-      <c r="H60">
-        <v>65</v>
-      </c>
-      <c r="I60">
-        <v>62</v>
-      </c>
-      <c r="J60">
-        <v>420</v>
-      </c>
-      <c r="K60">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>272</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61">
-        <v>231</v>
-      </c>
-      <c r="D61">
-        <v>326</v>
-      </c>
-      <c r="E61">
-        <v>5187</v>
-      </c>
-      <c r="F61">
-        <v>22</v>
-      </c>
-      <c r="G61">
-        <v>172</v>
-      </c>
-      <c r="H61">
-        <v>73</v>
-      </c>
-      <c r="I61">
-        <v>68</v>
-      </c>
-      <c r="J61">
-        <v>305</v>
-      </c>
-      <c r="K61">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>272</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>229</v>
-      </c>
-      <c r="D62">
-        <v>308</v>
-      </c>
-      <c r="E62">
-        <v>5456</v>
-      </c>
-      <c r="F62">
-        <v>22</v>
-      </c>
-      <c r="G62">
-        <v>168</v>
-      </c>
-      <c r="H62">
-        <v>75</v>
-      </c>
-      <c r="I62">
-        <v>74</v>
-      </c>
-      <c r="J62">
-        <v>351</v>
-      </c>
-      <c r="K62">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>272</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63">
-        <v>170</v>
-      </c>
-      <c r="D63">
-        <v>340</v>
-      </c>
-      <c r="E63">
-        <v>5483</v>
-      </c>
-      <c r="F63">
-        <v>20</v>
-      </c>
-      <c r="G63">
-        <v>173</v>
-      </c>
-      <c r="H63">
-        <v>64</v>
-      </c>
-      <c r="I63">
-        <v>67</v>
-      </c>
-      <c r="J63">
-        <v>307</v>
-      </c>
-      <c r="K63">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>272</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64">
-        <v>1701</v>
-      </c>
-      <c r="D64">
-        <v>421</v>
-      </c>
-      <c r="E64">
-        <v>11</v>
-      </c>
-      <c r="F64">
-        <v>671</v>
-      </c>
-      <c r="G64">
-        <v>46</v>
-      </c>
-      <c r="H64">
-        <v>174</v>
-      </c>
-      <c r="I64">
-        <v>71</v>
-      </c>
-      <c r="J64">
-        <v>128</v>
-      </c>
-      <c r="K64">
-        <v>367</v>
-      </c>
-      <c r="L64">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>272</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>364</v>
-      </c>
-      <c r="D65">
-        <v>258</v>
-      </c>
-      <c r="E65">
-        <v>7335</v>
-      </c>
-      <c r="F65">
-        <v>46</v>
-      </c>
-      <c r="G65">
-        <v>185</v>
-      </c>
-      <c r="H65">
-        <v>75</v>
-      </c>
-      <c r="I65">
-        <v>122</v>
-      </c>
-      <c r="J65">
-        <v>408</v>
-      </c>
-      <c r="K65">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>272</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66">
-        <v>682</v>
-      </c>
-      <c r="D66">
-        <v>300</v>
-      </c>
-      <c r="E66">
-        <v>7315</v>
-      </c>
-      <c r="F66">
-        <v>32</v>
-      </c>
-      <c r="G66">
-        <v>164</v>
-      </c>
-      <c r="H66">
-        <v>70</v>
-      </c>
-      <c r="I66">
-        <v>129</v>
-      </c>
-      <c r="J66">
-        <v>416</v>
-      </c>
-      <c r="K66">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>272</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>327</v>
-      </c>
-      <c r="D67">
-        <v>289</v>
-      </c>
-      <c r="E67">
-        <v>7512</v>
-      </c>
-      <c r="F67">
-        <v>37</v>
-      </c>
-      <c r="G67">
-        <v>181</v>
-      </c>
-      <c r="H67">
-        <v>71</v>
-      </c>
-      <c r="I67">
-        <v>126</v>
-      </c>
-      <c r="J67">
-        <v>459</v>
-      </c>
-      <c r="K67">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>272</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>326</v>
-      </c>
-      <c r="D68">
-        <v>286</v>
-      </c>
-      <c r="E68">
-        <v>7052</v>
-      </c>
-      <c r="F68">
-        <v>35</v>
-      </c>
-      <c r="G68">
-        <v>165</v>
-      </c>
-      <c r="H68">
-        <v>72</v>
-      </c>
-      <c r="I68">
-        <v>118</v>
-      </c>
-      <c r="J68">
-        <v>407</v>
-      </c>
-      <c r="K68">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>272</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69">
-        <v>331</v>
-      </c>
-      <c r="D69">
-        <v>296</v>
-      </c>
-      <c r="E69">
-        <v>7108</v>
-      </c>
-      <c r="F69">
-        <v>36</v>
-      </c>
-      <c r="G69">
-        <v>173</v>
-      </c>
-      <c r="H69">
-        <v>72</v>
-      </c>
-      <c r="I69">
-        <v>123</v>
-      </c>
-      <c r="J69">
-        <v>461</v>
-      </c>
-      <c r="K69">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>272</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70">
-        <v>2356</v>
-      </c>
-      <c r="D70">
-        <v>278</v>
-      </c>
-      <c r="E70">
-        <v>12</v>
-      </c>
-      <c r="F70">
-        <v>551</v>
-      </c>
-      <c r="G70">
-        <v>43</v>
-      </c>
-      <c r="H70">
-        <v>176</v>
-      </c>
-      <c r="I70">
-        <v>73</v>
-      </c>
-      <c r="J70">
-        <v>128</v>
-      </c>
-      <c r="K70">
-        <v>385</v>
-      </c>
-      <c r="L70">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>272</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71">
-        <v>2032</v>
-      </c>
-      <c r="D71">
-        <v>292</v>
-      </c>
-      <c r="E71">
-        <v>11</v>
-      </c>
-      <c r="F71">
-        <v>361</v>
-      </c>
-      <c r="G71">
-        <v>38</v>
-      </c>
-      <c r="H71">
-        <v>174</v>
-      </c>
-      <c r="I71">
-        <v>74</v>
-      </c>
-      <c r="J71">
-        <v>133</v>
-      </c>
-      <c r="K71">
-        <v>572</v>
-      </c>
-      <c r="L71">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>16</v>
       </c>
